--- a/Excels/Excels/__beans__.xlsx
+++ b/Excels/Excels/__beans__.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -43,45 +43,13 @@
       <family val="0"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <family val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <family val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFD0CECE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
-        <bgColor rgb="FFCCCCFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -93,7 +61,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="general" vertical="center"/>
     </xf>
@@ -102,14 +70,8 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
@@ -117,18 +79,6 @@
       <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="21">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -141,87 +91,81 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="21">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
     <cellStyle name="Currency" xfId="3" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
-    <cellStyle name="Excel Built-in Bad" xfId="6"/>
-    <cellStyle name="Excel Built-in Good" xfId="7"/>
   </cellStyles>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF9C0006"/>
-      <rgbColor rgb="FF006100"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFD0CECE"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFC7CE"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -405,542 +349,801 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="27.63" customWidth="1" style="8" min="2" max="2"/>
-    <col width="23.75" customWidth="1" style="8" min="3" max="3"/>
-    <col width="9.630000000000001" customWidth="1" style="9" min="4" max="4"/>
-    <col width="9.5" customWidth="1" style="8" min="5" max="5"/>
-    <col width="8.25" customWidth="1" style="8" min="6" max="6"/>
-    <col width="14.75" customWidth="1" style="8" min="7" max="7"/>
-    <col width="11.75" customWidth="1" style="8" min="8" max="8"/>
-    <col width="15" customWidth="1" style="8" min="9" max="9"/>
-    <col width="13.5" customWidth="1" style="8" min="10" max="11"/>
-    <col width="29.88" customWidth="1" style="8" min="12" max="12"/>
-    <col width="10.38" customWidth="1" style="8" min="13" max="13"/>
-    <col width="12.88" customWidth="1" style="8" min="14" max="14"/>
+    <col width="27.63" customWidth="1" style="4" min="2" max="2"/>
+    <col width="23.75" customWidth="1" style="4" min="3" max="3"/>
+    <col width="9.630000000000001" customWidth="1" style="5" min="4" max="4"/>
+    <col width="9.5" customWidth="1" style="4" min="5" max="5"/>
+    <col width="8.25" customWidth="1" style="4" min="6" max="6"/>
+    <col width="14.75" customWidth="1" style="4" min="7" max="7"/>
+    <col width="11.75" customWidth="1" style="4" min="8" max="8"/>
+    <col width="15" customWidth="1" style="4" min="9" max="9"/>
+    <col width="13.5" customWidth="1" style="4" min="10" max="11"/>
+    <col width="29.88" customWidth="1" style="4" min="12" max="12"/>
+    <col width="10.38" customWidth="1" style="4" min="13" max="13"/>
+    <col width="12.88" customWidth="1" style="4" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="10">
-      <c r="A1" s="11" t="inlineStr">
+    <row r="1" ht="14.25" customHeight="1" s="6">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>valueType</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>sep</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>alias</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>*fields</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="10">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="14.25" customHeight="1" s="6">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>alias</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="P2" s="8" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>variants</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="12.75" customHeight="1" s="10">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" ht="12.75" customHeight="1" s="6">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>全名(包含模块和名字)</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>分割符</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>字段名</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>字段别名</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>注释</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>字段变体</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" s="10">
-      <c r="B4" s="13" t="inlineStr">
+    <row r="4" ht="14.25" customHeight="1" s="6">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Attr.AttributePair</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>属性键值对</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Attr.AttributeType</t>
         </is>
       </c>
-      <c r="M4" s="13" t="n"/>
-      <c r="N4" s="13" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>属性类型</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" s="10">
-      <c r="J5" s="8" t="inlineStr">
+    <row r="5" ht="14.25" customHeight="1" s="6">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>属性值</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="7" ht="14.25" customHeight="1" s="10">
-      <c r="B7" s="13" t="inlineStr">
+    <row r="7" ht="14.25" customHeight="1" s="6">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Item.ItemPair</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>道具键值对</t>
         </is>
       </c>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="13" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>道具ID</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1" s="10">
-      <c r="J8" s="8" t="inlineStr">
+    <row r="8" ht="14.25" customHeight="1" s="6">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>道具数量</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10" ht="14.25" customHeight="1" s="10">
-      <c r="B10" s="13" t="inlineStr">
+    <row r="10" ht="14.25" customHeight="1" s="6">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Math.Weight</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>权重键值对</t>
         </is>
       </c>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1" s="10">
-      <c r="J11" s="8" t="inlineStr">
+    <row r="11" ht="14.25" customHeight="1" s="6">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>权重/概率</t>
         </is>
       </c>
     </row>
     <row r="12"/>
-    <row r="13" ht="14.25" customHeight="1" s="10">
-      <c r="B13" s="13" t="inlineStr">
+    <row r="13" ht="14.25" customHeight="1" s="6">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Math.Range</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>权重键值对</t>
         </is>
       </c>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="M13" s="13" t="n"/>
-      <c r="N13" s="13" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>最小值</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1" s="10">
-      <c r="J14" s="8" t="inlineStr">
+    <row r="14" ht="14.25" customHeight="1" s="6">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>最大值</t>
         </is>
       </c>
     </row>
     <row r="15"/>
-    <row r="16">
-      <c r="B16" t="inlineStr">
+    <row r="16" ht="14.25" customHeight="1" s="6">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Battle.EffectRef</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>效果引用</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Battle.EffectType</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="J17" t="inlineStr">
+    <row r="17" ht="14.25" customHeight="1" s="6">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="J18" t="inlineStr">
+    <row r="18" ht="14.25" customHeight="1" s="6">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
+    <row r="19"/>
+    <row r="20" ht="14.25" customHeight="1" s="6">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Battle.BattleShapeDesc</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>战斗范围形状</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>shapeType</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Battle.SkillShapeType</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="J21" t="inlineStr">
+    <row r="21" ht="14.25" customHeight="1" s="6">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="J22" t="inlineStr">
+    <row r="22" ht="14.25" customHeight="1" s="6">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="J23" t="inlineStr">
+    <row r="23" ht="14.25" customHeight="1" s="6">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>length</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="J24" t="inlineStr">
+    <row r="24" ht="14.25" customHeight="1" s="6">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>angleDeg</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="J25" t="inlineStr">
+    <row r="25" ht="14.25" customHeight="1" s="6">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>offsetX</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="J26" t="inlineStr">
+    <row r="26" ht="14.25" customHeight="1" s="6">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>offsetY</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28" ht="14.25" customHeight="1" s="6">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Battle.UnitSelector</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>单位筛选器</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>requiredUnitFlags</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Battle.UnitFlag</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>必须拥有的单位标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1" s="6">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>forbiddenUnitFlags</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Battle.UnitFlag</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>禁止拥有的单位标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1" s="6">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>requiredRoleFlags</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Battle.UnitRoleFlag</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>必须拥有的定位标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1" s="6">
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>forbiddenRoleFlags</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Battle.UnitRoleFlag</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>禁止拥有的定位标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1" s="6">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>unitCfgIds</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>(array#sep=|),int</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>允许的单位配置id</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34" ht="14.25" customHeight="1" s="6">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Battle.SkillSelector</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>技能筛选器</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>slotIndex</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>技能槽位，-1表示任意</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1" s="6">
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>skillIds</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>(array#sep=|),int</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>允许的技能id</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37" ht="14.25" customHeight="1" s="6">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Battle.ModifierValue</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>强化数值</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Attr.ValueType</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="14.25" customHeight="1" s="6">
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>intValue</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1" s="6"/>
+    <row r="40">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Battle.BattleModifierRef</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>强化引用</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>targetType</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>Battle.ModifierTargetType</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>目标类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1" s="6">
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>modifierType</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>目标对应的强化类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1" s="6">
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>Battle.ModifierValue</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>强化数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1" s="6">
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>Battle.EffectRef</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>可选效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1" s="6"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/Excels/Excels/__beans__.xlsx
+++ b/Excels/Excels/__beans__.xlsx
@@ -1068,7 +1068,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>,</t>
+          <t>;</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">

--- a/Excels/Excels/__beans__.xlsx
+++ b/Excels/Excels/__beans__.xlsx
@@ -349,7 +349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="27.63" customWidth="1" style="4" min="2" max="2"/>
@@ -945,205 +945,220 @@
     <row r="32" ht="14.25" customHeight="1" s="6">
       <c r="J32" s="4" t="inlineStr">
         <is>
+          <t>campType</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Battle.ModifierCampType</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>阵营筛选，默认玩家阵营</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="J33" s="4" t="inlineStr">
+        <is>
           <t>unitCfgIds</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>(array#sep=|),int</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>允许的单位配置id</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34" ht="14.25" customHeight="1" s="6">
-      <c r="B34" s="4" t="inlineStr">
+    <row r="34" ht="14.25" customHeight="1" s="6"/>
+    <row r="35" ht="14.25" customHeight="1" s="6">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Battle.SkillSelector</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>技能筛选器</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>slotIndex</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>技能槽位，-1表示任意</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="14.25" customHeight="1" s="6">
-      <c r="J35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>skillIds</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>(array#sep=|),int</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>允许的技能id</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37" ht="14.25" customHeight="1" s="6">
-      <c r="B37" s="4" t="inlineStr">
+    <row r="37" ht="14.25" customHeight="1" s="6"/>
+    <row r="38" ht="14.25" customHeight="1" s="6">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Battle.ModifierValue</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>强化数值</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>Attr.ValueType</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1" s="6">
-      <c r="J38" s="4" t="inlineStr">
+    <row r="39" ht="14.25" customHeight="1" s="6">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>intValue</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="14.25" customHeight="1" s="6"/>
-    <row r="40">
-      <c r="B40" s="4" t="inlineStr">
+    <row r="41" ht="14.25" customHeight="1" s="6">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Battle.BattleModifierRef</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>;</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>强化引用</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>targetType</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>Battle.ModifierTargetType</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>目标类型</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1" s="6">
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>modifierType</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>目标对应的强化类型</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="6">
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>modifierType</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>Battle.ModifierValue</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>强化数值</t>
+          <t>目标对应的强化类型</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="6">
       <c r="J43" s="4" t="inlineStr">
         <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>Battle.ModifierValue</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>强化数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1" s="6">
+      <c r="J44" s="4" t="inlineStr">
+        <is>
           <t>effect</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>Battle.EffectRef</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>可选效果</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="14.25" customHeight="1" s="6"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
